--- a/experiment/Omni+CNN_2CH_bestx4/results_HUTCN_Omni+CNN_2CH_bestx4.xlsx
+++ b/experiment/Omni+CNN_2CH_bestx4/results_HUTCN_Omni+CNN_2CH_bestx4.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5225,7 +5225,7 @@
       <c r="D281" t="n">
         <v>0.02488</v>
       </c>
-      <c r="E281" s="3" t="n">
+      <c r="E281" s="2" t="n">
         <v>32.545</v>
       </c>
     </row>
@@ -5567,6 +5567,1876 @@
       </c>
       <c r="E301" t="n">
         <v>32.452</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="E302" t="n">
+        <v>32.071</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="E303" t="n">
+        <v>32.467</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E304" t="n">
+        <v>32.475</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E305" t="n">
+        <v>32.512</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E306" t="n">
+        <v>32.491</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="E307" t="n">
+        <v>32.515</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="E308" t="n">
+        <v>32.543</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.02475</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.02475</v>
+      </c>
+      <c r="E309" t="n">
+        <v>32.527</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.02488</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.02488</v>
+      </c>
+      <c r="E310" t="n">
+        <v>32.508</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="E311" t="n">
+        <v>32.472</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="E312" t="n">
+        <v>32.516</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="E313" t="n">
+        <v>32.345</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="E314" t="n">
+        <v>32.527</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="E315" t="n">
+        <v>32.458</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="E316" t="n">
+        <v>32.522</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.02422999999999999</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.02422999999999999</v>
+      </c>
+      <c r="E317" t="n">
+        <v>32.324</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="E318" t="n">
+        <v>32.49</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="E319" t="n">
+        <v>32.487</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="E320" t="n">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="E321" t="n">
+        <v>32.325</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>32.565</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E323" t="n">
+        <v>32.517</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.02459</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.02459</v>
+      </c>
+      <c r="E324" t="n">
+        <v>32.478</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="E325" t="n">
+        <v>32.504</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E326" t="n">
+        <v>32.513</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E327" t="n">
+        <v>32.487</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.02439</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.02439</v>
+      </c>
+      <c r="E328" t="n">
+        <v>32.557</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="E329" t="n">
+        <v>32.552</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="E330" t="n">
+        <v>32.51</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="E331" t="n">
+        <v>32.172</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="E332" t="n">
+        <v>32.467</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.02482</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.02482</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>32.567</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.02447</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.02447</v>
+      </c>
+      <c r="E334" t="n">
+        <v>32.411</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="E335" t="n">
+        <v>32.56</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.02464</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.02464</v>
+      </c>
+      <c r="E336" t="n">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.02425</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.02425</v>
+      </c>
+      <c r="E337" t="n">
+        <v>32.437</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="E338" t="n">
+        <v>32.511</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.02508</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.02508</v>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="E340" t="n">
+        <v>32.544</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="E341" t="n">
+        <v>32.49</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.02444</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.02444</v>
+      </c>
+      <c r="E342" t="n">
+        <v>32.513</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="E343" t="n">
+        <v>32.561</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.02508</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.02508</v>
+      </c>
+      <c r="E344" t="n">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="E345" t="n">
+        <v>32.253</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E346" t="n">
+        <v>32.512</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="E347" t="n">
+        <v>32.499</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="E348" t="n">
+        <v>32.475</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E349" t="n">
+        <v>32.521</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="E350" t="n">
+        <v>32.558</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.02493</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.02493</v>
+      </c>
+      <c r="E351" t="n">
+        <v>32.536</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="E352" t="n">
+        <v>32.364</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E353" t="n">
+        <v>32.459</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="E354" t="n">
+        <v>32.456</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="E355" t="n">
+        <v>32.517</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.02456</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.02456</v>
+      </c>
+      <c r="E356" t="n">
+        <v>32.497</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="E357" t="n">
+        <v>32.52</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.02469</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.02469</v>
+      </c>
+      <c r="E358" t="n">
+        <v>32.493</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="E359" t="n">
+        <v>32.528</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="E360" t="n">
+        <v>32.491</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="E361" t="n">
+        <v>32.482</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E362" t="n">
+        <v>32.475</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.02444</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.02444</v>
+      </c>
+      <c r="E363" t="n">
+        <v>32.456</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="E364" t="n">
+        <v>32.516</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.02427</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.02427</v>
+      </c>
+      <c r="E365" t="n">
+        <v>32.513</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="E366" t="n">
+        <v>32.534</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="E367" t="n">
+        <v>32.546</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="E368" t="n">
+        <v>32.563</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="E369" t="n">
+        <v>32.523</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.02441</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.02441</v>
+      </c>
+      <c r="E370" t="n">
+        <v>32.504</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="E371" t="n">
+        <v>32.525</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="E372" t="n">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="E373" t="n">
+        <v>32.547</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.02441</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.02441</v>
+      </c>
+      <c r="E374" t="n">
+        <v>32.542</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="E375" t="n">
+        <v>32.474</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.02446</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.02446</v>
+      </c>
+      <c r="E376" t="n">
+        <v>32.465</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.02471</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.02471</v>
+      </c>
+      <c r="E377" t="n">
+        <v>32.542</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="E378" t="n">
+        <v>32.531</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.02488</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.02488</v>
+      </c>
+      <c r="E379" t="n">
+        <v>32.542</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="E380" t="n">
+        <v>32.557</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="E381" t="n">
+        <v>32.453</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="E382" t="n">
+        <v>32.391</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="E383" t="n">
+        <v>32.481</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.02503</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.02503</v>
+      </c>
+      <c r="E384" t="n">
+        <v>32.528</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="E385" t="n">
+        <v>32.508</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="E386" t="n">
+        <v>32.547</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E387" t="n">
+        <v>32.549</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E388" t="n">
+        <v>32.528</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="E389" t="n">
+        <v>32.567</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="E390" t="n">
+        <v>32.499</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.02473</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.02473</v>
+      </c>
+      <c r="E391" t="n">
+        <v>32.547</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.02429</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.02429</v>
+      </c>
+      <c r="E392" t="n">
+        <v>32.553</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="E393" t="n">
+        <v>32.517</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="E394" t="n">
+        <v>32.513</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="E395" t="n">
+        <v>32.501</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.02445</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.02445</v>
+      </c>
+      <c r="E396" t="n">
+        <v>32.467</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="E397" t="n">
+        <v>32.535</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.02492</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.02492</v>
+      </c>
+      <c r="E398" t="n">
+        <v>32.533</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="E399" t="n">
+        <v>32.539</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="E400" t="n">
+        <v>32.524</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="E401" t="n">
+        <v>32.55</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="E402" t="n">
+        <v>32.533</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.02463</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.02463</v>
+      </c>
+      <c r="E403" t="n">
+        <v>32.525</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="E404" t="n">
+        <v>32.559</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="E405" t="n">
+        <v>32.474</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="E406" t="n">
+        <v>32.465</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.02484</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.02484</v>
+      </c>
+      <c r="E407" t="n">
+        <v>32.511</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="E408" t="n">
+        <v>32.51</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="E409" t="n">
+        <v>32.32</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0.02462</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.02462</v>
+      </c>
+      <c r="E410" t="n">
+        <v>32.564</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>0.000497</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="E411" t="n">
+        <v>32.534</v>
       </c>
     </row>
   </sheetData>
